--- a/VerveStacks_CHN_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E61C96A-A727-4718-9CCD-140183FC9729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19AA3E5-3A6B-4ECC-83B5-8AB131A9C54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4898,7 +4898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822BB5A5-ADA7-4E57-A933-B59CF4CE104C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5847E661-B7DB-481B-A312-683A63C99E36}">
   <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19AA3E5-3A6B-4ECC-83B5-8AB131A9C54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E099B6-435D-49D7-9DEA-4876C8DFEB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4898,7 +4898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5847E661-B7DB-481B-A312-683A63C99E36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023F1B8D-F264-429F-8DA3-94D1467430DD}">
   <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
